--- a/Demo web shop project/Test_Execution.xlsx
+++ b/Demo web shop project/Test_Execution.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C53D3281-65D2-4824-B1D1-D455ED7FCE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D119F799-1F5B-4C57-8594-253A5F4C6AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,112 +31,271 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
-  <si>
-    <t>S.No</t>
-  </si>
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>Test Case Name</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>TC_001</t>
-  </si>
-  <si>
-    <t>Login with valid credentials</t>
-  </si>
-  <si>
-    <t>User logged in successfully</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>TC_002</t>
-  </si>
-  <si>
-    <t>Login with Invalid credentials</t>
-  </si>
-  <si>
-    <t>Error message displayed</t>
-  </si>
-  <si>
-    <t>TC_003</t>
-  </si>
-  <si>
-    <t>Login with empty fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TC_004</t>
-  </si>
-  <si>
-    <t>Verify forgot password functionality</t>
-  </si>
-  <si>
-    <t>Email not received</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>TC_005</t>
-  </si>
-  <si>
-    <t>Add product to Cart</t>
-  </si>
-  <si>
-    <t>Cart displays added products successfully</t>
-  </si>
-  <si>
-    <t>TC_006</t>
-  </si>
-  <si>
-    <t>Verify cart displays added product</t>
-  </si>
-  <si>
-    <t>Cart displayed added products</t>
-  </si>
-  <si>
-    <t>TC_007</t>
-  </si>
-  <si>
-    <t>Add product to Wish list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product added to wishlist successfully </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="84">
+  <si>
+    <t xml:space="preserve">TC_ID </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test Case Name </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Actual Result </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Login with valid credentials </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User logged in successfully </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_002 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Login with invalid credentials </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Error message displayed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_003 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Login with empty fields </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validation message displayed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_004 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Forgot password functionality </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recovery email not received </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_005 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add product to cart </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product added to cart successfully </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_006 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify cart displays product </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product displayed correctly in cart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_007 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add product to wishlist </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product added to wishlist successfully </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_008 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logout functionality </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User logged out successfully </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_009 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Login with case sensitive password </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Login failed as expected </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_010 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Login with unregistered email </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Search valid product </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Relevant products displayed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_012 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Search invalid product </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No results message displayed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Search with special characters </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> System handled input without crash </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify product listing </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Products displayed correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify product price display </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product prices displayed correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify category navigation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Category products displayed correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_017 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify product details page </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product details displayed correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add to cart from product page </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product added successfully </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_019 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Remove product from cart </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product removed successfully </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_020 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Update cart quantity </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quantity updated correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_021 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify empty cart message </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Empty cart message displayed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_022 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Remove product from wishlist </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_023 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add same product twice to wishlist </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Duplicate product not added </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_024 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify user account page </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Account details displayed correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Register user with valid data </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User registered successfully </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Register with existing email </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_027 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Proceed to checkout </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Navigated to checkout page </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -159,10 +318,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -170,96 +327,9 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="1">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -275,14 +345,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5E9C1974-FEFC-4E35-9A89-9FAECDF14DBF}" name="Table2" displayName="Table2" ref="H9:L16" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="H9:L16" xr:uid="{5E9C1974-FEFC-4E35-9A89-9FAECDF14DBF}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{13857F5F-7CA2-4032-8371-F5744D800594}" name="S.No" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{8155A558-0722-47DE-90E5-BC9EB0DA4062}" name="Test Case ID" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{6D9BBACC-24BE-4CAB-B579-4B1F89345652}" name="Test Case Name" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{B805F750-310E-41CE-B54D-D3E4BBBB938D}" name="Actual result"/>
-    <tableColumn id="5" xr3:uid="{23D241C6-B5C9-4B1E-B930-F4E114353917}" name="Status"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8F6C1960-4050-4AD2-94E3-4EE5E1E321C9}" name="Table1" displayName="Table1" ref="C5:F33" totalsRowShown="0">
+  <autoFilter ref="C5:F33" xr:uid="{8F6C1960-4050-4AD2-94E3-4EE5E1E321C9}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{4A8CEEF6-1029-451E-AF8E-9B322B3B3D13}" name="TC_ID " dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{878268BC-29CE-48F2-BDFC-30DE1DCE0838}" name=" Test Case Name "/>
+    <tableColumn id="3" xr3:uid="{0311C2DB-E9B3-488F-B0A6-4358382DBF4F}" name=" Actual Result "/>
+    <tableColumn id="4" xr3:uid="{4DF11BD1-3ADC-4052-AC02-FE1D837B5FE1}" name=" Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -605,249 +674,409 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="G9:L46"/>
+  <dimension ref="C5:F33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="7" max="7" width="30.5703125" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="7:12">
-      <c r="G9" s="1"/>
-      <c r="H9" s="2" t="s">
+    <row r="5" spans="3:6">
+      <c r="C5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="D5" t="s">
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="E5" t="s">
         <v>2</v>
       </c>
-      <c r="K9" t="s">
+      <c r="F5" t="s">
         <v>3</v>
       </c>
-      <c r="L9" t="s">
+    </row>
+    <row r="6" spans="3:6">
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="3:6">
+      <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="7:12">
-      <c r="G10" s="1"/>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="D7" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="E7" t="s">
         <v>6</v>
       </c>
-      <c r="K10" t="s">
-        <v>7</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6">
+      <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="7:12">
-      <c r="G11" s="1"/>
-      <c r="H11" s="2">
-        <v>2</v>
-      </c>
-      <c r="I11" s="2" t="s">
+      <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="E8" t="s">
         <v>10</v>
       </c>
-      <c r="K11" t="s">
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6">
+      <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="7:12">
-      <c r="G12" s="1"/>
-      <c r="H12" s="2">
-        <v>3</v>
-      </c>
-      <c r="I12" s="2" t="s">
+      <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="E9" t="s">
         <v>13</v>
       </c>
-      <c r="K12" t="s">
-        <v>11</v>
-      </c>
-      <c r="L12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="7:12">
-      <c r="G13" s="1"/>
-      <c r="H13" s="2">
-        <v>4</v>
-      </c>
-      <c r="I13" s="1" t="s">
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6">
+      <c r="C10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="D10" t="s">
         <v>15</v>
       </c>
-      <c r="K13" t="s">
+      <c r="E10" t="s">
         <v>16</v>
       </c>
-      <c r="L13" t="s">
+      <c r="F10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="12.75" customHeight="1">
-      <c r="G14" s="1"/>
-      <c r="H14" s="2">
-        <v>5</v>
-      </c>
-      <c r="I14" s="2" t="s">
+    <row r="11" spans="3:6">
+      <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="D11" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="L14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="7:12">
-      <c r="G15" s="1"/>
-      <c r="H15" s="2">
-        <v>6</v>
-      </c>
-      <c r="I15" s="2" t="s">
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6">
+      <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="D12" t="s">
         <v>22</v>
       </c>
-      <c r="K15" t="s">
+      <c r="E12" t="s">
         <v>23</v>
       </c>
-      <c r="L15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="7:12">
-      <c r="G16" s="1"/>
-      <c r="H16" s="2">
-        <v>7</v>
-      </c>
-      <c r="I16" s="2" t="s">
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6">
+      <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="D13" t="s">
         <v>25</v>
       </c>
-      <c r="K16" t="s">
+      <c r="E13" t="s">
         <v>26</v>
       </c>
-      <c r="L16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="7:7">
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="7:7">
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="7:7">
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="7:7">
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="7:7">
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="7:7">
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="7:7">
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="7:7">
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="7:7">
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="7:7">
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="7:7">
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="7:7">
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="7:7">
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="7:7">
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="7:7">
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="7:7">
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="7:7">
-      <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="7:7">
-      <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="7:7">
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="7:7">
-      <c r="G36" s="1"/>
-    </row>
-    <row r="37" spans="7:7">
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="7:7">
-      <c r="G38" s="1"/>
-    </row>
-    <row r="39" spans="7:7">
-      <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="7:7">
-      <c r="G40" s="1"/>
-    </row>
-    <row r="41" spans="7:7">
-      <c r="G41" s="1"/>
-    </row>
-    <row r="42" spans="7:7">
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="7:7">
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="7:7">
-      <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="7:7">
-      <c r="G45" s="1"/>
-    </row>
-    <row r="46" spans="7:7">
-      <c r="G46" s="1"/>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6">
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6">
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6">
+      <c r="C16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6">
+      <c r="C17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6">
+      <c r="C18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6">
+      <c r="C19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6">
+      <c r="C20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6">
+      <c r="C21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6">
+      <c r="C22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6">
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6">
+      <c r="C24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6">
+      <c r="C25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6">
+      <c r="C26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6">
+      <c r="C27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6">
+      <c r="C28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6">
+      <c r="C29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6">
+      <c r="C30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="3:6">
+      <c r="C31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="3:6">
+      <c r="C32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6">
+      <c r="C33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
